--- a/Output/Tables/table1_by_PHC.xlsx
+++ b/Output/Tables/table1_by_PHC.xlsx
@@ -351,42 +351,42 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>[ALL]   N=2058</t>
+          <t>[ALL]   N=1963</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Borrell   N=410</t>
+          <t>Borrell   N=395</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Casanova   N=299</t>
+          <t>Casanova   N=260</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Montnegre_1   N=202</t>
+          <t>Montnegre_1   N=194</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Montnegre_2   N=165</t>
+          <t>Montnegre_2   N=159</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Marc_Aureli   N=298</t>
+          <t>Marc_Aureli   N=292</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Sant_Elies   N=351</t>
+          <t>Sant_Elies   N=344</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Lluch   N=333</t>
+          <t>Lluch   N=319</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -403,47 +403,47 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1573 (76.4%)  </t>
+          <t xml:space="preserve">  1490 (75.9%)  </t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  329 (80.2%)   </t>
+          <t xml:space="preserve">  314 (79.5%)   </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  226 (75.6%)   </t>
+          <t xml:space="preserve">  194 (74.6%)   </t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  151 (74.8%)   </t>
+          <t xml:space="preserve">  143 (73.7%)   </t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  121 (73.3%)   </t>
+          <t xml:space="preserve">  118 (74.2%)   </t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  221 (74.2%)   </t>
+          <t xml:space="preserve">  215 (73.6%)   </t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  269 (76.6%)   </t>
+          <t xml:space="preserve">  263 (76.5%)   </t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  256 (76.9%)   </t>
+          <t xml:space="preserve">  243 (76.2%)   </t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  0.479  </t>
+          <t xml:space="preserve">  0.586  </t>
         </is>
       </c>
     </row>
@@ -455,47 +455,47 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1475 (71.7%)  </t>
+          <t xml:space="preserve">  1397 (71.2%)  </t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  296 (72.2%)   </t>
+          <t xml:space="preserve">  284 (71.9%)   </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  235 (78.6%)   </t>
+          <t xml:space="preserve">  199 (76.5%)   </t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  125 (61.9%)   </t>
+          <t xml:space="preserve">  119 (61.3%)   </t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  116 (70.3%)   </t>
+          <t xml:space="preserve">  112 (70.4%)   </t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  212 (71.1%)   </t>
+          <t xml:space="preserve">  208 (71.2%)   </t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  257 (73.2%)   </t>
+          <t xml:space="preserve">  250 (72.7%)   </t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  234 (70.3%)   </t>
+          <t xml:space="preserve">  225 (70.5%)   </t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  0.007  </t>
+          <t xml:space="preserve">  0.037  </t>
         </is>
       </c>
     </row>
@@ -507,47 +507,47 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">  88.7 (10.1)   </t>
+          <t xml:space="preserve">  88.7 (10.0)   </t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">  87.8 (9.20)   </t>
+          <t xml:space="preserve">  87.7 (9.27)   </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">  90.6 (8.08)   </t>
+          <t xml:space="preserve">  90.4 (8.19)   </t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">  87.3 (12.4)   </t>
+          <t xml:space="preserve">  87.7 (11.8)   </t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">  89.0 (9.90)   </t>
+          <t xml:space="preserve">  89.0 (9.77)   </t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">  89.7 (10.1)   </t>
+          <t xml:space="preserve">  89.8 (10.1)   </t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t xml:space="preserve">  87.9 (11.9)   </t>
+          <t xml:space="preserve">  87.9 (12.0)   </t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t xml:space="preserve">  89.0 (8.79)   </t>
+          <t xml:space="preserve">  89.1 (8.49)   </t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> &lt;0.001  </t>
+          <t xml:space="preserve">  0.003  </t>
         </is>
       </c>
     </row>
@@ -559,47 +559,47 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3.19 (3.12)   </t>
+          <t xml:space="preserve">  3.17 (3.12)   </t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3.00 (2.44)   </t>
+          <t xml:space="preserve">  3.05 (2.46)   </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3.01 (2.33)   </t>
+          <t xml:space="preserve">  2.90 (2.18)   </t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3.09 (3.71)   </t>
+          <t xml:space="preserve">  3.12 (3.78)   </t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3.87 (4.34)   </t>
+          <t xml:space="preserve">  3.78 (4.33)   </t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3.23 (3.23)   </t>
+          <t xml:space="preserve">  3.21 (3.23)   </t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3.37 (3.81)   </t>
+          <t xml:space="preserve">  3.34 (3.82)   </t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3.08 (2.39)   </t>
+          <t xml:space="preserve">  3.05 (2.21)   </t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  0.205  </t>
+          <t xml:space="preserve">  0.111  </t>
         </is>
       </c>
     </row>
@@ -611,47 +611,47 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1933 (93.9%)  </t>
+          <t xml:space="preserve">  1840 (93.7%)  </t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  391 (95.4%)   </t>
+          <t xml:space="preserve">  376 (95.2%)   </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  283 (94.6%)   </t>
+          <t xml:space="preserve">  246 (94.6%)   </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  184 (91.1%)   </t>
+          <t xml:space="preserve">  176 (90.7%)   </t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  155 (93.9%)   </t>
+          <t xml:space="preserve">  149 (93.7%)   </t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  278 (93.3%)   </t>
+          <t xml:space="preserve">  272 (93.2%)   </t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  319 (90.9%)   </t>
+          <t xml:space="preserve">  312 (90.7%)   </t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  323 (97.0%)   </t>
+          <t xml:space="preserve">  309 (96.9%)   </t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  0.014  </t>
+          <t xml:space="preserve">  0.016  </t>
         </is>
       </c>
     </row>
@@ -663,42 +663,42 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">  11.4 (4.55)   </t>
+          <t xml:space="preserve">  11.4 (4.56)   </t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">  11.1 (4.14)   </t>
+          <t xml:space="preserve">  11.1 (4.17)   </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">  11.8 (4.19)   </t>
+          <t xml:space="preserve">  11.7 (4.12)   </t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">  11.0 (4.77)   </t>
+          <t xml:space="preserve">  11.0 (4.80)   </t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">  10.7 (4.20)   </t>
+          <t xml:space="preserve">  10.8 (4.26)   </t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">  11.2 (4.72)   </t>
+          <t xml:space="preserve">  11.2 (4.76)   </t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">  10.7 (4.70)   </t>
+          <t xml:space="preserve">  10.6 (4.71)   </t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t xml:space="preserve">  13.2 (4.62)   </t>
+          <t xml:space="preserve">  13.2 (4.55)   </t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -720,37 +720,37 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  19.1 (7.44)   </t>
+          <t xml:space="preserve">  19.1 (7.49)   </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  19.2 (7.64)   </t>
+          <t xml:space="preserve">  19.2 (7.57)   </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  18.7 (8.55)   </t>
+          <t xml:space="preserve">  18.8 (8.62)   </t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  18.2 (7.52)   </t>
+          <t xml:space="preserve">  18.4 (7.60)   </t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  18.7 (8.08)   </t>
+          <t xml:space="preserve">  18.7 (8.15)   </t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  18.0 (8.53)   </t>
+          <t xml:space="preserve">  17.9 (8.57)   </t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  23.0 (8.29)   </t>
+          <t xml:space="preserve">  22.9 (8.14)   </t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  0.34 (0.12)   </t>
+          <t xml:space="preserve">  0.34 (0.13)   </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  0.40 (0.16)   </t>
+          <t xml:space="preserve">  0.39 (0.17)   </t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -797,17 +797,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
+          <t xml:space="preserve">  0.37 (0.14)   </t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
           <t xml:space="preserve">  0.38 (0.14)   </t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  0.38 (0.14)   </t>
-        </is>
-      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  0.081  </t>
+          <t xml:space="preserve">  0.185  </t>
         </is>
       </c>
     </row>
@@ -819,42 +819,42 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1585 (77.0%)  </t>
+          <t xml:space="preserve">  1511 (77.0%)  </t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  336 (82.0%)   </t>
+          <t xml:space="preserve">  323 (81.8%)   </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  167 (55.9%)   </t>
+          <t xml:space="preserve">  140 (53.8%)   </t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  161 (79.7%)   </t>
+          <t xml:space="preserve">  153 (78.9%)   </t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  124 (75.2%)   </t>
+          <t xml:space="preserve">  120 (75.5%)   </t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  232 (77.9%)   </t>
+          <t xml:space="preserve">  227 (77.7%)   </t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  289 (82.3%)   </t>
+          <t xml:space="preserve">  284 (82.6%)   </t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  276 (82.9%)   </t>
+          <t xml:space="preserve">  264 (82.8%)   </t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -871,47 +871,47 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  162 (7.87%)   </t>
+          <t xml:space="preserve">  159 (8.10%)   </t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">   41 (10.0%)   </t>
+          <t xml:space="preserve">   41 (10.4%)   </t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">   31 (10.4%)   </t>
+          <t xml:space="preserve">   30 (11.5%)   </t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">   16 (7.92%)   </t>
+          <t xml:space="preserve">   16 (8.25%)   </t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">   11 (6.67%)   </t>
+          <t xml:space="preserve">   11 (6.92%)   </t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">   20 (6.71%)   </t>
+          <t xml:space="preserve">   20 (6.85%)   </t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">   19 (5.41%)   </t>
+          <t xml:space="preserve">   18 (5.23%)   </t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t xml:space="preserve">   24 (7.21%)   </t>
+          <t xml:space="preserve">   23 (7.21%)   </t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  0.166  </t>
+          <t xml:space="preserve">  0.063  </t>
         </is>
       </c>
     </row>
@@ -975,42 +975,42 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">  215 (10.4%)   </t>
+          <t xml:space="preserve">  204 (10.4%)   </t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">   30 (7.32%)   </t>
+          <t xml:space="preserve">   29 (7.34%)   </t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">   30 (10.0%)   </t>
+          <t xml:space="preserve">   24 (9.23%)   </t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">   18 (8.91%)   </t>
+          <t xml:space="preserve">   16 (8.25%)   </t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">   23 (13.9%)   </t>
+          <t xml:space="preserve">   22 (13.8%)   </t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">   39 (13.1%)   </t>
+          <t xml:space="preserve">   39 (13.4%)   </t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">   35 (9.97%)   </t>
+          <t xml:space="preserve">   35 (10.2%)   </t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t xml:space="preserve">   40 (12.0%)   </t>
+          <t xml:space="preserve">   39 (12.2%)   </t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1027,42 +1027,42 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">  261 (12.7%)   </t>
+          <t xml:space="preserve">  248 (12.6%)   </t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">   54 (13.2%)   </t>
+          <t xml:space="preserve">   53 (13.4%)   </t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">   42 (14.0%)   </t>
+          <t xml:space="preserve">   36 (13.8%)   </t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">   20 (9.90%)   </t>
+          <t xml:space="preserve">   20 (10.3%)   </t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">   27 (16.4%)   </t>
+          <t xml:space="preserve">   25 (15.7%)   </t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">   47 (15.8%)   </t>
+          <t xml:space="preserve">   46 (15.8%)   </t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">   38 (10.8%)   </t>
+          <t xml:space="preserve">   36 (10.5%)   </t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t xml:space="preserve">   33 (9.91%)   </t>
+          <t xml:space="preserve">   32 (10.0%)   </t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1079,42 +1079,42 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  476 (23.1%)   </t>
+          <t xml:space="preserve">  453 (23.1%)   </t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">   75 (18.3%)   </t>
+          <t xml:space="preserve">   72 (18.2%)   </t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">   80 (26.8%)   </t>
+          <t xml:space="preserve">   69 (26.5%)   </t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">   37 (18.3%)   </t>
+          <t xml:space="preserve">   35 (18.0%)   </t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">   37 (22.4%)   </t>
+          <t xml:space="preserve">   36 (22.6%)   </t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">   69 (23.2%)   </t>
+          <t xml:space="preserve">   68 (23.3%)   </t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  109 (31.1%)   </t>
+          <t xml:space="preserve">  107 (31.1%)   </t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t xml:space="preserve">   69 (20.7%)   </t>
+          <t xml:space="preserve">   66 (20.7%)   </t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1131,42 +1131,42 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1031 (50.1%)  </t>
+          <t xml:space="preserve">  988 (50.3%)   </t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  248 (60.5%)   </t>
+          <t xml:space="preserve">  238 (60.3%)   </t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  139 (46.5%)   </t>
+          <t xml:space="preserve">  125 (48.1%)   </t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  111 (55.0%)   </t>
+          <t xml:space="preserve">  108 (55.7%)   </t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   67 (40.6%)   </t>
+          <t xml:space="preserve">   66 (41.5%)   </t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  133 (44.6%)   </t>
+          <t xml:space="preserve">  129 (44.2%)   </t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  151 (43.0%)   </t>
+          <t xml:space="preserve">  148 (43.0%)   </t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  182 (54.7%)   </t>
+          <t xml:space="preserve">  174 (54.5%)   </t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1183,42 +1183,42 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   31 (1.51%)   </t>
+          <t xml:space="preserve">   29 (1.48%)   </t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   1 (0.24%)    </t>
+          <t xml:space="preserve">   1 (0.25%)    </t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   4 (1.34%)    </t>
+          <t xml:space="preserve">   3 (1.15%)    </t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   7 (3.47%)    </t>
+          <t xml:space="preserve">   6 (3.09%)    </t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   1 (0.61%)    </t>
+          <t xml:space="preserve">   1 (0.63%)    </t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   5 (1.68%)    </t>
+          <t xml:space="preserve">   5 (1.71%)    </t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   8 (2.28%)    </t>
+          <t xml:space="preserve">   8 (2.33%)    </t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   5 (1.50%)    </t>
+          <t xml:space="preserve">   5 (1.57%)    </t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1235,42 +1235,42 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   44 (2.14%)   </t>
+          <t xml:space="preserve">   41 (2.09%)   </t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   2 (0.49%)    </t>
+          <t xml:space="preserve">   2 (0.51%)    </t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   4 (1.34%)    </t>
+          <t xml:space="preserve">   3 (1.15%)    </t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   9 (4.46%)    </t>
+          <t xml:space="preserve">   9 (4.64%)    </t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   10 (6.06%)   </t>
+          <t xml:space="preserve">   9 (5.66%)    </t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   5 (1.68%)    </t>
+          <t xml:space="preserve">   5 (1.71%)    </t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   10 (2.85%)   </t>
+          <t xml:space="preserve">   10 (2.91%)   </t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   4 (1.20%)    </t>
+          <t xml:space="preserve">   3 (0.94%)    </t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t xml:space="preserve">  0.009  </t>
+          <t xml:space="preserve">  0.007  </t>
         </is>
       </c>
     </row>
@@ -1339,42 +1339,42 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1095 (53.2%)  </t>
+          <t xml:space="preserve">  1052 (53.6%)  </t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">  225 (54.9%)   </t>
+          <t xml:space="preserve">  218 (55.2%)   </t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">  161 (53.8%)   </t>
+          <t xml:space="preserve">  142 (54.6%)   </t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">  109 (54.0%)   </t>
+          <t xml:space="preserve">  105 (54.1%)   </t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">   84 (50.9%)   </t>
+          <t xml:space="preserve">   83 (52.2%)   </t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">  144 (48.3%)   </t>
+          <t xml:space="preserve">  141 (48.3%)   </t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">  197 (56.1%)   </t>
+          <t xml:space="preserve">  195 (56.7%)   </t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t xml:space="preserve">  175 (52.6%)   </t>
+          <t xml:space="preserve">  168 (52.7%)   </t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1391,42 +1391,42 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">  301 (14.6%)   </t>
+          <t xml:space="preserve">  289 (14.7%)   </t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">   70 (17.1%)   </t>
+          <t xml:space="preserve">   68 (17.2%)   </t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">   38 (12.7%)   </t>
+          <t xml:space="preserve">   35 (13.5%)   </t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">   26 (12.9%)   </t>
+          <t xml:space="preserve">   24 (12.4%)   </t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">   24 (14.5%)   </t>
+          <t xml:space="preserve">   24 (15.1%)   </t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">   45 (15.1%)   </t>
+          <t xml:space="preserve">   44 (15.1%)   </t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">   49 (14.0%)   </t>
+          <t xml:space="preserve">   48 (14.0%)   </t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t xml:space="preserve">   49 (14.7%)   </t>
+          <t xml:space="preserve">   46 (14.4%)   </t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1443,42 +1443,42 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">  275 (13.4%)   </t>
+          <t xml:space="preserve">  257 (13.1%)   </t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">   49 (12.0%)   </t>
+          <t xml:space="preserve">   46 (11.6%)   </t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">   44 (14.7%)   </t>
+          <t xml:space="preserve">   36 (13.8%)   </t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">   29 (14.4%)   </t>
+          <t xml:space="preserve">   27 (13.9%)   </t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">   21 (12.7%)   </t>
+          <t xml:space="preserve">   21 (13.2%)   </t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">   48 (16.1%)   </t>
+          <t xml:space="preserve">   47 (16.1%)   </t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">   47 (13.4%)   </t>
+          <t xml:space="preserve">   46 (13.4%)   </t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t xml:space="preserve">   37 (11.1%)   </t>
+          <t xml:space="preserve">   34 (10.7%)   </t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1495,42 +1495,42 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">  335 (16.3%)   </t>
+          <t xml:space="preserve">  316 (16.1%)   </t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">   63 (15.4%)   </t>
+          <t xml:space="preserve">   60 (15.2%)   </t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">   49 (16.4%)   </t>
+          <t xml:space="preserve">   41 (15.8%)   </t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">   29 (14.4%)   </t>
+          <t xml:space="preserve">   29 (14.9%)   </t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">   24 (14.5%)   </t>
+          <t xml:space="preserve">   20 (12.6%)   </t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">   55 (18.5%)   </t>
+          <t xml:space="preserve">   54 (18.5%)   </t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">   47 (13.4%)   </t>
+          <t xml:space="preserve">   44 (12.8%)   </t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t xml:space="preserve">   68 (20.4%)   </t>
+          <t xml:space="preserve">   68 (21.3%)   </t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1547,42 +1547,42 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">   52 (2.53%)   </t>
+          <t xml:space="preserve">   49 (2.50%)   </t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">   3 (0.73%)    </t>
+          <t xml:space="preserve">   3 (0.76%)    </t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">   7 (2.34%)    </t>
+          <t xml:space="preserve">   6 (2.31%)    </t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">   9 (4.46%)    </t>
+          <t xml:space="preserve">   9 (4.64%)    </t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">   12 (7.27%)   </t>
+          <t xml:space="preserve">   11 (6.92%)   </t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">   6 (2.01%)    </t>
+          <t xml:space="preserve">   6 (2.05%)    </t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">   11 (3.13%)   </t>
+          <t xml:space="preserve">   11 (3.20%)   </t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t xml:space="preserve">   4 (1.20%)    </t>
+          <t xml:space="preserve">   3 (0.94%)    </t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t xml:space="preserve"> &lt;0.001  </t>
+          <t xml:space="preserve">  0.001  </t>
         </is>
       </c>
     </row>
@@ -1651,42 +1651,42 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">  252 (12.2%)   </t>
+          <t xml:space="preserve">  242 (12.3%)   </t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">   34 (8.29%)   </t>
+          <t xml:space="preserve">   34 (8.61%)   </t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">   47 (15.7%)   </t>
+          <t xml:space="preserve">   40 (15.4%)   </t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">   23 (11.4%)   </t>
+          <t xml:space="preserve">   23 (11.9%)   </t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">   24 (14.5%)   </t>
+          <t xml:space="preserve">   22 (13.8%)   </t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">   25 (8.39%)   </t>
+          <t xml:space="preserve">   25 (8.56%)   </t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">   42 (12.0%)   </t>
+          <t xml:space="preserve">   41 (11.9%)   </t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t xml:space="preserve">   57 (17.1%)   </t>
+          <t xml:space="preserve">   57 (17.9%)   </t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1703,22 +1703,22 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t xml:space="preserve">   8 (0.39%)    </t>
+          <t xml:space="preserve">   8 (0.41%)    </t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">   4 (0.98%)    </t>
+          <t xml:space="preserve">   4 (1.01%)    </t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">   2 (0.67%)    </t>
+          <t xml:space="preserve">   2 (0.77%)    </t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">   1 (0.50%)    </t>
+          <t xml:space="preserve">   1 (0.52%)    </t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t xml:space="preserve">   1 (0.30%)    </t>
+          <t xml:space="preserve">   1 (0.31%)    </t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -1755,42 +1755,42 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1044 (50.7%)  </t>
+          <t xml:space="preserve">  992 (50.5%)   </t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">  232 (56.6%)   </t>
+          <t xml:space="preserve">  222 (56.2%)   </t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">  163 (54.5%)   </t>
+          <t xml:space="preserve">  139 (53.5%)   </t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">   90 (44.6%)   </t>
+          <t xml:space="preserve">   86 (44.3%)   </t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">   84 (50.9%)   </t>
+          <t xml:space="preserve">   82 (51.6%)   </t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">  144 (48.3%)   </t>
+          <t xml:space="preserve">  141 (48.3%)   </t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t xml:space="preserve">  174 (49.6%)   </t>
+          <t xml:space="preserve">  172 (50.0%)   </t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t xml:space="preserve">  157 (47.1%)   </t>
+          <t xml:space="preserve">  150 (47.0%)   </t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -1807,42 +1807,42 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">  754 (36.6%)   </t>
+          <t xml:space="preserve">  721 (36.7%)   </t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">  140 (34.1%)   </t>
+          <t xml:space="preserve">  135 (34.2%)   </t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">   87 (29.1%)   </t>
+          <t xml:space="preserve">   79 (30.4%)   </t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">   88 (43.6%)   </t>
+          <t xml:space="preserve">   84 (43.3%)   </t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">   57 (34.5%)   </t>
+          <t xml:space="preserve">   55 (34.6%)   </t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">  129 (43.3%)   </t>
+          <t xml:space="preserve">  126 (43.2%)   </t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">  135 (38.5%)   </t>
+          <t xml:space="preserve">  131 (38.1%)   </t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t xml:space="preserve">  118 (35.4%)   </t>
+          <t xml:space="preserve">  111 (34.8%)   </t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -1911,42 +1911,42 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1008 (49.0%)  </t>
+          <t xml:space="preserve">  961 (49.0%)   </t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">  341 (83.2%)   </t>
+          <t xml:space="preserve">  328 (83.0%)   </t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">  161 (53.8%)   </t>
+          <t xml:space="preserve">  143 (55.0%)   </t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">   94 (46.5%)   </t>
+          <t xml:space="preserve">   88 (45.4%)   </t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">   51 (30.9%)   </t>
+          <t xml:space="preserve">   49 (30.8%)   </t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">  106 (35.6%)   </t>
+          <t xml:space="preserve">  104 (35.6%)   </t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">  163 (46.4%)   </t>
+          <t xml:space="preserve">  162 (47.1%)   </t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve">   92 (27.6%)   </t>
+          <t xml:space="preserve">   87 (27.3%)   </t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -1963,42 +1963,42 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve">  241 (11.7%)   </t>
+          <t xml:space="preserve">  219 (11.2%)   </t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">   55 (13.4%)   </t>
+          <t xml:space="preserve">   53 (13.4%)   </t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">   99 (33.1%)   </t>
+          <t xml:space="preserve">   84 (32.3%)   </t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">   7 (3.47%)    </t>
+          <t xml:space="preserve">   6 (3.09%)    </t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">   12 (7.27%)   </t>
+          <t xml:space="preserve">   12 (7.55%)   </t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">   23 (7.72%)   </t>
+          <t xml:space="preserve">   21 (7.19%)   </t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">   29 (8.26%)   </t>
+          <t xml:space="preserve">   28 (8.14%)   </t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t xml:space="preserve">   16 (4.80%)   </t>
+          <t xml:space="preserve">   15 (4.70%)   </t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2015,42 +2015,42 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t xml:space="preserve">  809 (39.3%)   </t>
+          <t xml:space="preserve">  783 (39.9%)   </t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">   14 (3.41%)   </t>
+          <t xml:space="preserve">   14 (3.54%)   </t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">   39 (13.0%)   </t>
+          <t xml:space="preserve">   33 (12.7%)   </t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">  101 (50.0%)   </t>
+          <t xml:space="preserve">  100 (51.5%)   </t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">  102 (61.8%)   </t>
+          <t xml:space="preserve">   98 (61.6%)   </t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">  169 (56.7%)   </t>
+          <t xml:space="preserve">  167 (57.2%)   </t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">  159 (45.3%)   </t>
+          <t xml:space="preserve">  154 (44.8%)   </t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t xml:space="preserve">  225 (67.6%)   </t>
+          <t xml:space="preserve">  217 (68.0%)   </t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2067,47 +2067,47 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t xml:space="preserve">  0.52 (0.95)   </t>
+          <t xml:space="preserve">  0.51 (0.95)   </t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve">  0.62 (0.98)   </t>
+          <t xml:space="preserve">  0.62 (0.99)   </t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">  0.37 (0.76)   </t>
+          <t xml:space="preserve">  0.37 (0.74)   </t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">  0.53 (1.01)   </t>
+          <t xml:space="preserve">  0.49 (0.95)   </t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">  0.53 (1.09)   </t>
+          <t xml:space="preserve">  0.53 (1.10)   </t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">  0.42 (0.95)   </t>
+          <t xml:space="preserve">  0.41 (0.94)   </t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t xml:space="preserve">  0.49 (1.00)   </t>
+          <t xml:space="preserve">  0.48 (0.99)   </t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t xml:space="preserve">  0.63 (0.91)   </t>
+          <t xml:space="preserve">  0.62 (0.92)   </t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t xml:space="preserve">  0.001  </t>
+          <t xml:space="preserve">  0.005  </t>
         </is>
       </c>
     </row>
@@ -2119,42 +2119,42 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t xml:space="preserve">  397 (19.3%)   </t>
+          <t xml:space="preserve">  374 (19.1%)   </t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t xml:space="preserve">  127 (31.0%)   </t>
+          <t xml:space="preserve">  125 (31.6%)   </t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">   61 (20.4%)   </t>
+          <t xml:space="preserve">   51 (19.6%)   </t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">   16 (7.92%)   </t>
+          <t xml:space="preserve">   13 (6.70%)   </t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">   26 (15.8%)   </t>
+          <t xml:space="preserve">   25 (15.7%)   </t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">   54 (18.1%)   </t>
+          <t xml:space="preserve">   53 (18.2%)   </t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">   53 (15.1%)   </t>
+          <t xml:space="preserve">   52 (15.1%)   </t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t xml:space="preserve">   60 (18.0%)   </t>
+          <t xml:space="preserve">   55 (17.2%)   </t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2171,42 +2171,42 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t xml:space="preserve">  535 (26.0%)   </t>
+          <t xml:space="preserve">  505 (25.7%)   </t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t xml:space="preserve">  164 (40.0%)   </t>
+          <t xml:space="preserve">  157 (39.7%)   </t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">   75 (25.1%)   </t>
+          <t xml:space="preserve">   63 (24.2%)   </t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">   42 (20.8%)   </t>
+          <t xml:space="preserve">   38 (19.6%)   </t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">   31 (18.8%)   </t>
+          <t xml:space="preserve">   30 (18.9%)   </t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">   69 (23.2%)   </t>
+          <t xml:space="preserve">   69 (23.6%)   </t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">   64 (18.2%)   </t>
+          <t xml:space="preserve">   62 (18.0%)   </t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t xml:space="preserve">   90 (27.0%)   </t>
+          <t xml:space="preserve">   86 (27.0%)   </t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>9.00 [5.00;15.0]</t>
+          <t>9.00 [5.00;15.2]</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2243,22 +2243,22 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>6.00 [3.00;11.0]</t>
+          <t>6.00 [3.00;12.0]</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>5.00 [3.00;8.00]</t>
+          <t>5.00 [3.00;9.00]</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>4.00 [2.00;6.50]</t>
+          <t>4.00 [2.00;6.00]</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>9.00 [6.00;18.0]</t>
+          <t>9.00 [6.00;18.5]</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>16.0 [9.00;27.0]</t>
+          <t>16.0 [9.50;27.0]</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>17.0 [9.00;29.0]</t>
+          <t>17.0 [10.0;29.0]</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2295,7 +2295,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>6.00 [3.00;17.0]</t>
+          <t>6.00 [3.00;17.5]</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>16.0 [10.0;27.0]</t>
+          <t>16.0 [10.0;27.5]</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2327,27 +2327,27 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t xml:space="preserve">77.1 [52.1;100] </t>
+          <t xml:space="preserve">77.8 [52.9;100] </t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t xml:space="preserve">94.4 [85.7;100] </t>
+          <t xml:space="preserve">95.0 [85.7;100] </t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>71.6 [57.1;85.1]</t>
+          <t>71.4 [57.1;85.0]</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">74.5 [50.0;100] </t>
+          <t xml:space="preserve">75.0 [50.0;100] </t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">76.5 [50.0;100] </t>
+          <t xml:space="preserve">77.8 [51.0;100] </t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>52.9 [33.3;85.7]</t>
+          <t>52.7 [33.3;85.7]</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>70.0 [55.0;85.7]</t>
+          <t>70.5 [55.6;85.7]</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2.00 [1.00;4.00]</t>
+          <t>2.00 [1.00;4.25]</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>11.0 [5.00;18.0]</t>
+          <t>12.0 [5.00;18.0]</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>23.0 [14.0;36.0]</t>
+          <t>24.0 [14.0;36.0]</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2483,22 +2483,22 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>46.2 [22.2;69.9]</t>
+          <t>45.9 [21.4;69.5]</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>50.0 [35.7;63.6]</t>
+          <t>50.0 [35.5;65.7]</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>50.0 [32.7;72.7]</t>
+          <t>50.0 [32.8;69.1]</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>16.7 [0.00;50.0]</t>
+          <t>17.4 [0.00;50.0]</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2508,17 +2508,17 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>46.0 [0.00;83.3]</t>
+          <t>44.4 [0.00;83.3]</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>36.4 [0.00;87.5]</t>
+          <t>36.0 [0.00;87.5]</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>60.0 [43.8;75.9]</t>
+          <t>60.0 [44.1;76.0]</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2545,12 +2545,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>13.0 [8.00;21.5]</t>
+          <t>13.0 [8.00;21.2]</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>8.00 [4.00;16.0]</t>
+          <t>8.00 [4.00;15.8]</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>6.00 [3.00;11.0]</t>
+          <t>6.00 [3.00;10.2]</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>19.0 [12.0;32.0]</t>
+          <t>19.0 [13.0;32.0]</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -2592,27 +2592,27 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>29.0 [18.0;45.0]</t>
+          <t>29.0 [17.5;45.0]</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>30.0 [17.0;46.5]</t>
+          <t>31.0 [17.0;48.0]</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>12.0 [6.00;23.0]</t>
+          <t>11.5 [6.00;22.8]</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>10.0 [6.00;24.0]</t>
+          <t>10.0 [6.00;24.5]</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>9.00 [6.00;16.0]</t>
+          <t>9.00 [5.75;16.0]</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2622,7 +2622,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>42.0 [27.0;67.0]</t>
+          <t>43.0 [28.0;67.0]</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -2639,27 +2639,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t xml:space="preserve">88.2 [72.7;100] </t>
+          <t xml:space="preserve">88.5 [73.3;100] </t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t xml:space="preserve">96.9 [92.0;100] </t>
+          <t xml:space="preserve">97.2 [92.3;100] </t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>83.3 [73.5;91.7]</t>
+          <t>83.3 [74.2;91.4]</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">83.3 [62.7;100] </t>
+          <t xml:space="preserve">83.3 [63.3;100] </t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">84.6 [66.7;100] </t>
+          <t xml:space="preserve">85.2 [67.9;100] </t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2669,12 +2669,12 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">76.9 [54.2;100] </t>
+          <t xml:space="preserve">75.4 [54.2;100] </t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>88.9 [80.3;94.6]</t>
+          <t>89.2 [80.8;94.7]</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.00 [0.00;3.00]</t>
+          <t>1.00 [0.00;2.00]</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2763,19 +2763,19 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
+          <t>1.00 [0.00;2.00]</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.00 [0.00;1.00]</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
           <t>0.00 [0.00;2.00]</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>0.00 [0.00;1.00]</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>0.00 [0.00;2.00]</t>
-        </is>
-      </c>
       <c r="I47" t="inlineStr">
         <is>
           <t>1.00 [0.00;2.00]</t>
@@ -2783,7 +2783,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t xml:space="preserve"> &lt;0.001  </t>
+          <t xml:space="preserve">  0.002  </t>
         </is>
       </c>
     </row>
@@ -2835,7 +2835,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t xml:space="preserve">  0.003  </t>
+          <t xml:space="preserve">  0.006  </t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t xml:space="preserve">   258 (156)    </t>
+          <t xml:space="preserve">   259 (156)    </t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2857,17 +2857,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">   233 (156)    </t>
+          <t xml:space="preserve">   229 (156)    </t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">   242 (162)    </t>
+          <t xml:space="preserve">   242 (163)    </t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">   264 (155)    </t>
+          <t xml:space="preserve">   265 (155)    </t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">   267 (158)    </t>
+          <t xml:space="preserve">   269 (158)    </t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t xml:space="preserve">   254 (153)    </t>
+          <t xml:space="preserve">   257 (153)    </t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -2899,32 +2899,32 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t xml:space="preserve">   294 (146)    </t>
+          <t xml:space="preserve">   295 (146)    </t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t xml:space="preserve">   286 (146)    </t>
+          <t xml:space="preserve">   288 (145)    </t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">   277 (150)    </t>
+          <t xml:space="preserve">   275 (150)    </t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">   279 (157)    </t>
+          <t xml:space="preserve">   281 (157)    </t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">   311 (144)    </t>
+          <t xml:space="preserve">   310 (144)    </t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">   319 (136)    </t>
+          <t xml:space="preserve">   318 (137)    </t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2934,12 +2934,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve">   292 (146)    </t>
+          <t xml:space="preserve">   296 (145)    </t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t xml:space="preserve">  0.004  </t>
+          <t xml:space="preserve">  0.012  </t>
         </is>
       </c>
     </row>
@@ -2956,42 +2956,42 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t xml:space="preserve">   310 (141)    </t>
+          <t xml:space="preserve">   311 (140)    </t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">   312 (139)    </t>
+          <t xml:space="preserve">   307 (143)    </t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">   328 (135)    </t>
+          <t xml:space="preserve">   329 (135)    </t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">   327 (132)    </t>
+          <t xml:space="preserve">   324 (133)    </t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">   341 (125)    </t>
+          <t xml:space="preserve">   340 (126)    </t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">   337 (126)    </t>
+          <t xml:space="preserve">   338 (126)    </t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t xml:space="preserve">   319 (135)    </t>
+          <t xml:space="preserve">   324 (133)    </t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t xml:space="preserve">  0.011  </t>
+          <t xml:space="preserve">  0.013  </t>
         </is>
       </c>
     </row>
